--- a/docs/Test_Report/Cdd_Ipc/TestPlanExecutionReport_Cdd_Ipc.xlsx
+++ b/docs/Test_Report/Cdd_Ipc/TestPlanExecutionReport_Cdd_Ipc.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Template Revision History" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000FF"/>
+        <fgColor rgb="00D3D3D3"/>
       </patternFill>
     </fill>
     <fill>
@@ -724,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774,MCAL-30778</t>
+          <t>MCAL-32372,MCAL-32370</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09 10:43:46.158087-05:00 CDT</t>
+          <t>2025-08-29 04:37:23.899713-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1362,17 +1362,17 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>62</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="7" t="inlineStr">
@@ -1381,11 +1381,24 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>62</v>
-      </c>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1396,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U63"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1532,12 +1545,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1648,12 +1661,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1667,12 +1680,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1783,12 +1796,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1802,12 +1815,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1878,7 +1891,23 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[IPC Performance] IPC Transmission data per second",
+                    "unit": "bytes",
+                    "value_type": "int",
+                    "description": " IPC Transmission data per second",
+                    "group": "IPC Performance",
+                    "benchmark": 2146692,
+                    "benchmark_delta": 10000
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -1914,12 +1943,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1933,12 +1962,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2048,12 +2077,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2067,12 +2096,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2183,12 +2212,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2202,12 +2231,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2317,12 +2346,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2336,12 +2365,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2452,12 +2481,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2471,12 +2500,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2587,12 +2616,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2606,12 +2635,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2720,12 +2749,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2739,12 +2768,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2853,12 +2882,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2872,12 +2901,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2986,12 +3015,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -3005,12 +3034,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3119,12 +3148,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3138,12 +3167,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3250,12 +3279,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3269,12 +3298,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3381,12 +3410,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3400,12 +3429,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3514,12 +3543,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3533,12 +3562,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3645,12 +3674,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3664,12 +3693,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3776,12 +3805,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3795,12 +3824,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3908,12 +3937,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3927,12 +3956,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4039,12 +4068,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4058,12 +4087,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4171,12 +4200,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4190,12 +4219,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4303,12 +4332,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4322,12 +4351,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4434,12 +4463,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4453,12 +4482,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4566,12 +4595,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4585,12 +4614,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4697,12 +4726,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4716,12 +4745,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4828,12 +4857,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4847,12 +4876,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4959,12 +4988,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4978,12 +5007,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5090,12 +5119,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5109,12 +5138,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5221,12 +5250,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5240,12 +5269,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5352,12 +5381,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5371,12 +5400,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5485,12 +5514,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5504,12 +5533,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5616,12 +5645,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5635,12 +5664,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5747,12 +5776,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5766,12 +5795,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5880,12 +5909,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5899,12 +5928,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -6011,12 +6040,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6030,12 +6059,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6142,12 +6171,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6161,12 +6190,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6273,12 +6302,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6292,12 +6321,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6404,12 +6433,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6423,12 +6452,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6535,12 +6564,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6554,12 +6583,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6666,12 +6695,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6685,12 +6714,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6797,12 +6826,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6816,12 +6845,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6928,12 +6957,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -6947,12 +6976,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7059,12 +7088,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -7078,12 +7107,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7190,12 +7219,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -7209,12 +7238,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7321,12 +7350,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -7340,12 +7369,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7452,12 +7481,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -7471,12 +7500,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -7583,12 +7612,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -7602,12 +7631,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7714,12 +7743,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -7733,12 +7762,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7846,12 +7875,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -7865,12 +7894,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -7977,12 +8006,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -7996,12 +8025,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30772</t>
+          <t>MCAL-32371</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Automated Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -8108,12 +8137,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30774</t>
+          <t>MCAL-32372</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Automated Tests Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -8127,55 +8156,155 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30777</t>
+          <t>MCAL-32369</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
+          <t>MCAL-32154</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Test to check the configurability of CddIpcUserCallbackFunction in configurator.</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30568</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm,F29P58x-evm</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Test to check the configurability of CddIpcUserCallbackFunction in configurator.
+CddIpcUserCallbackFunction shouldn't be redeclared in  Cdd_Ipc_Cbk when same CddIpcUserCallbackFunction is configured for different channels.</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>CddIpcUserCallbackFunction shouldn't be redeclared in  Cdd_Ipc_Cbk when same CddIpcUserCallbackFunction is configured for different channels.</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>CDD IPC</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
           <t>MCAL-29851</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Qualification test : Test to check the below functionality Between CPU1 and CPU2 with TX &amp; Rx in both ISR and polling mode:Init,sync,read counter,Tx,Rx,Ack.</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>MCAL-30156,MCAL-30154,MCAL-30159,MCAL-30155,MCAL-30157,MCAL-30161</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>IPC complete functionality of TX and RX</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">The CDD IPC driver should implement 
 1.baisc TX &amp; Rx functionality in ISR mode
@@ -8184,101 +8313,101 @@
 </t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N52" s="3" t="inlineStr">
+      <c r="N53" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
+      <c r="O53" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P52" s="3" t="inlineStr">
+      <c r="P53" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q52" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R52" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S52" s="3" t="inlineStr"/>
-      <c r="T52" s="3" t="inlineStr"/>
-      <c r="U52" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>MCAL-29850</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Qualification test : Test to check the below functionality Between CPU1 and CPU2 with instance 3:Init,sync,read counter,TxRx in ISR mode(mode set by remote core),Ack.</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>MCAL-30155,MCAL-30157,MCAL-30154,MCAL-30156,MCAL-30159,MCAL-30161</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>IPC complete functionality of TX and RX</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">The CDD IPC driver should implement 
 1.baisc TX &amp; Rx functionality in ISR mode
@@ -8287,391 +8416,391 @@
 </t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N53" s="3" t="inlineStr">
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
+      <c r="O54" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P53" s="3" t="inlineStr">
+      <c r="P54" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q53" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R53" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S53" s="3" t="inlineStr"/>
-      <c r="T53" s="3" t="inlineStr"/>
-      <c r="U53" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29843</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Qualification Test : CDD IPC Driver AUTOSAR 4.3.1 requirements:1.Complex Driver design and integration guideline.2.General Requirements on Basic Software Modules</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30153</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>The CDD IPC driver should implement AUTOSAR 4.3.1 requirements.</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The CDD IPC driver should implement AUTOSAR 4.3.1 requirements.
-</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="inlineStr">
-        <is>
-          <t>CDD IPC</t>
-        </is>
-      </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30778</t>
+          <t>MCAL-32370</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
       <c r="T54" s="3" t="inlineStr"/>
       <c r="U54" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30777</t>
+          <t>MCAL-32369</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
+          <t>MCAL-29843</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Qualification Test : CDD IPC Driver AUTOSAR 4.3.1 requirements:1.Complex Driver design and integration guideline.2.General Requirements on Basic Software Modules</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30153</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>The CDD IPC driver should implement AUTOSAR 4.3.1 requirements.</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The CDD IPC driver should implement AUTOSAR 4.3.1 requirements.
+</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>CDD IPC</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
           <t>MCAL-29838</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Test to check whether CddIpc Tx channel symbolic names are present in generated file.</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>MCAL-30603</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Test to check symbolic name for:
 CddIpc Tx channel
  </t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>All configured CddIpc Tx channel's should have symbolic names in generated Code</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr">
+      <c r="M56" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N55" s="3" t="inlineStr">
+      <c r="N56" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="O56" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P55" s="3" t="inlineStr">
+      <c r="P56" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q55" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R55" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S55" s="3" t="inlineStr"/>
-      <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29830</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Integration Test to check configurable options using a configuration plugin that is compatible with an AUTOSAR based configurator tool are present.</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Architecture,Architecture,Architecture</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30172,MCAL-30163,MCAL-30171</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>Check Cdd Ipc driver provides its configurable options using a configuration plugin</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>A configuration plugin shoube be provided that is compatible with an AUTOSAR based configurator tool. It should support Pre-Compile configuration variant.</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="inlineStr">
-        <is>
-          <t>CDD IPC</t>
-        </is>
-      </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30778</t>
+          <t>MCAL-32370</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
       <c r="T56" s="3" t="inlineStr"/>
-      <c r="U56" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U56" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30777</t>
+          <t>MCAL-32369</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
+          <t>MCAL-29830</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test to check configurable options using a configuration plugin that is compatible with an AUTOSAR based configurator tool are present.</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Architecture,Architecture,Architecture</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30172,MCAL-30163,MCAL-30171</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Check Cdd Ipc driver provides its configurable options using a configuration plugin</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>A configuration plugin shoube be provided that is compatible with an AUTOSAR based configurator tool. It should support Pre-Compile configuration variant.</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>CDD IPC</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
           <t>MCAL-29813</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Test to check whether Configuration parameters are present in configurator.</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>MCAL-30551,MCAL-30552,MCAL-30554,MCAL-30557,MCAL-30558,MCAL-30569,MCAL-30570,MCAL-30572,MCAL-30575,MCAL-30576,MCAL-30559,MCAL-30563,MCAL-30566,MCAL-30556,MCAL-30553,MCAL-30555,MCAL-30561,MCAL-30573,MCAL-30550,MCAL-30562,MCAL-30564,MCAL-30565,MCAL-30567,MCAL-30568,MCAL-30574,MCAL-30560,MCAL-30571</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>Test to check Configuration parameter exists for:
 CddIpcDevErrorDetect
@@ -8698,101 +8827,101 @@
 CddPduRLowerLayerPduRef</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="K58" s="3" t="inlineStr">
         <is>
           <t>All mentioned containers should exist in xdm and configurator</t>
         </is>
       </c>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M57" s="3" t="inlineStr">
+      <c r="M58" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N57" s="3" t="inlineStr">
+      <c r="N58" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
+      <c r="O58" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P57" s="3" t="inlineStr">
+      <c r="P58" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q57" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R57" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S57" s="3" t="inlineStr"/>
-      <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>MCAL-29812</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Test to check whether Configuration Container are present in configurator</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>MCAL-30542,MCAL-30544,MCAL-30547,MCAL-30539,MCAL-30540,MCAL-30541,MCAL-30543,MCAL-30545,MCAL-30548,MCAL-30549,MCAL-30546</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>Test to check Configuration Container exists for:
 CddIpcGeneral
@@ -8810,501 +8939,501 @@
 CddIpcRxChannelConfig</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>All mentioned containers should exist in xdm and configurator</t>
         </is>
       </c>
-      <c r="L58" s="3" t="inlineStr">
+      <c r="L59" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr">
+      <c r="M59" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N58" s="3" t="inlineStr">
+      <c r="N59" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
+      <c r="O59" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P58" s="3" t="inlineStr">
+      <c r="P59" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q58" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R58" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S58" s="3" t="inlineStr"/>
-      <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>MCAL-29811</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Test to check whether symbolic names are present in generated file</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>MCAL-30538</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>Test to check symbolic name for:
 PduR Lower layer Tx PdU's</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>All configured PduR Lower layer Tx PdU's should have symbolic names in generated Code</t>
         </is>
       </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
+      <c r="M60" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N59" s="3" t="inlineStr">
+      <c r="N60" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
+      <c r="O60" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P59" s="3" t="inlineStr">
+      <c r="P60" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q59" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S59" s="3" t="inlineStr"/>
-      <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>MCAL-29810</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Test to check whether symbolic names are present in generated file.</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>MCAL-30537</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>Test to check symbolic name for:
 PduR Lower layer Rx PdU's</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>All configured PduR Lower layer Rx PdU's should have symbolic names in generated Code</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="L61" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="M61" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N60" s="3" t="inlineStr">
+      <c r="N61" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
+      <c r="O61" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P60" s="3" t="inlineStr">
+      <c r="P61" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q60" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R60" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S60" s="3" t="inlineStr"/>
-      <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>MCAL-29809</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Test to check whether symbolic names are present in generated file</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>MCAL-30536</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>Test to check symbolic name for:
 configured  remote cores</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>All configured remote cores should have symbolic names in generated Code</t>
         </is>
       </c>
-      <c r="L61" s="3" t="inlineStr">
+      <c r="L62" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
+      <c r="M62" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N61" s="3" t="inlineStr">
+      <c r="N62" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
+      <c r="O62" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P61" s="3" t="inlineStr">
+      <c r="P62" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R61" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S61" s="3" t="inlineStr"/>
-      <c r="T61" s="3" t="inlineStr"/>
-      <c r="U61" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>MCAL-29808</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Test to check whether global variable is present or not.</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>MCAL-30533,MCAL-30535,MCAL-30534</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>Test to check:
 Cdd_Ipc_IsInitialized</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>All global variables should be present in Code</t>
         </is>
       </c>
-      <c r="L62" s="3" t="inlineStr">
+      <c r="L63" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
+      <c r="M63" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N62" s="3" t="inlineStr">
+      <c r="N63" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
+      <c r="O63" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P62" s="3" t="inlineStr">
+      <c r="P63" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q62" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R62" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S62" s="3" t="inlineStr"/>
-      <c r="T62" s="3" t="inlineStr"/>
-      <c r="U62" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30777</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : CDD IPC- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32369</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : CDD IPC- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>MCAL-29807</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Test to check whether all data types are present or not.</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>MCAL-30520,MCAL-30527,MCAL-30529,MCAL-30518,MCAL-30531,MCAL-30525,MCAL-30530,MCAL-30532,MCAL-30519,MCAL-30528,MCAL-30521,MCAL-30524,MCAL-30522,MCAL-30523,MCAL-30526</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>Test to check:
 Cdd_Ipc_NotifyType
@@ -9319,61 +9448,61 @@
 Cdd_Ipc_RxChannelConfig</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>All Datatypes and arrays should be present in Code</t>
         </is>
       </c>
-      <c r="L63" s="3" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M63" s="3" t="inlineStr">
+      <c r="M64" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N63" s="3" t="inlineStr">
+      <c r="N64" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
+      <c r="O64" s="3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="P63" s="3" t="inlineStr">
+      <c r="P64" s="3" t="inlineStr">
         <is>
           <t>CDD IPC</t>
         </is>
       </c>
-      <c r="Q63" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30778</t>
-        </is>
-      </c>
-      <c r="R63" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: CDD_IPC - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S63" s="3" t="inlineStr"/>
-      <c r="T63" s="3" t="inlineStr"/>
-      <c r="U63" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32370</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00: CDD_IPC - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U63"/>
+  <autoFilter ref="A1:U64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
